--- a/todo_list.xlsx
+++ b/todo_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/avisek/Git_Repositary/decode-labs_internship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A446CD38-0EA2-E242-BD0D-928F054EF2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDAC3E16-69EC-9647-965C-FD8F3B39ED65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Task ID</t>
   </si>
@@ -50,6 +50,28 @@
   </si>
   <si>
     <t>Completed</t>
+  </si>
+  <si>
+    <t>Data Cleaning &amp; Preparation</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>DA001</t>
+  </si>
+  <si>
+    <t>Goal:
+Clean a raw dataset by handling missing values, duplicates, and incorrect data.
+Key Requirements:
+• Identify missing or null values
+• Remove duplicates
+• Correct data formats (dates, numbers, text)
+Key Skills:
+Data cleaning, Excel or Python basics, data preparation</t>
   </si>
 </sst>
 </file>
@@ -91,12 +113,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -399,14 +430,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="30" customWidth="1"/>
+    <col min="7" max="7" width="65" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -444,6 +475,32 @@
       </c>
       <c r="E2" s="2">
         <v>46101</v>
+      </c>
+      <c r="F2" s="2">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="128" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="5">
+        <v>46105</v>
+      </c>
+      <c r="F3" s="5">
+        <v>46109</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/todo_list.xlsx
+++ b/todo_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/avisek/Git_Repositary/decode-labs_internship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDAC3E16-69EC-9647-965C-FD8F3B39ED65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C949F1-9BC4-6449-B5E2-31D60577F1D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>Task ID</t>
   </si>
@@ -43,28 +43,26 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>Project 1</t>
-  </si>
-  <si>
     <t>Low</t>
   </si>
   <si>
     <t>Completed</t>
   </si>
   <si>
-    <t>Data Cleaning &amp; Preparation</t>
-  </si>
-  <si>
     <t>High</t>
   </si>
   <si>
-    <t>In Progress</t>
-  </si>
-  <si>
     <t>DA001</t>
   </si>
   <si>
-    <t>Goal:
+    <t>Completion Date</t>
+  </si>
+  <si>
+    <t>Project 1 Introduction</t>
+  </si>
+  <si>
+    <t>Data Cleaning &amp; Preparation 
+Goal:
 Clean a raw dataset by handling missing values, duplicates, and incorrect data.
 Key Requirements:
 • Identify missing or null values
@@ -73,12 +71,20 @@
 Key Skills:
 Data cleaning, Excel or Python basics, data preparation</t>
   </si>
+  <si>
+    <t xml:space="preserve">Missing Values replaced by Forword Fill
+No Duplicates found
+Data formats okay
+Used Python for data cleaning
+File saved as dataset for Data Analysis_V1.1.xlsx
+</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -88,8 +94,14 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -113,20 +125,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -430,17 +443,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="65" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="56.6640625" style="2" customWidth="1"/>
+    <col min="3" max="7" width="20.83203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="65.83203125" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -457,49 +470,58 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B2" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" s="3">
+        <v>46101</v>
+      </c>
+      <c r="F2" s="3">
+        <v>46101</v>
+      </c>
+      <c r="G2" s="3">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="221" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2">
-        <v>46101</v>
-      </c>
-      <c r="F2" s="2">
-        <v>46101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="128" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>11</v>
-      </c>
       <c r="D3" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E3" s="5">
         <v>46105</v>
       </c>
       <c r="F3" s="5">
+        <v>46105</v>
+      </c>
+      <c r="G3" s="5">
         <v>46109</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="6" t="s">
         <v>14</v>
       </c>
     </row>

--- a/todo_list.xlsx
+++ b/todo_list.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/avisek/Git_Repositary/decode-labs_internship/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/avisek/Git_Repositary/DecodeLabs-Internship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C949F1-9BC4-6449-B5E2-31D60577F1D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC693AA-B908-A040-B24B-AF2C8988BBE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,9 +34,6 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Recv Date</t>
-  </si>
-  <si>
     <t>Due Date</t>
   </si>
   <si>
@@ -50,9 +47,6 @@
   </si>
   <si>
     <t>High</t>
-  </si>
-  <si>
-    <t>DA001</t>
   </si>
   <si>
     <t>Completion Date</t>
@@ -72,9 +66,18 @@
 Data cleaning, Excel or Python basics, data preparation</t>
   </si>
   <si>
-    <t xml:space="preserve">Missing Values replaced by Forword Fill
+    <t>Assign Date</t>
+  </si>
+  <si>
+    <t>DCLB_DA001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Missing Values replaced by Forword Fill Method
 No Duplicates found
 Data formats okay
+outliers detected &amp; removed with upper bound 
+Histogram for data distribution
+Correlation
 Used Python for data cleaning
 File saved as dataset for Data Analysis_V1.1.xlsx
 </t>
@@ -446,7 +449,7 @@
   <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="14.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="56.6640625" style="2" customWidth="1"/>
     <col min="3" max="7" width="20.83203125" style="2" customWidth="1"/>
     <col min="8" max="8" width="65.83203125" style="2" customWidth="1"/>
@@ -467,27 +470,27 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="E2" s="3">
         <v>46101</v>
@@ -501,22 +504,22 @@
     </row>
     <row r="3" spans="1:8" ht="221" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" s="5">
         <v>46105</v>
       </c>
       <c r="F3" s="5">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="G3" s="5">
         <v>46109</v>

--- a/todo_list.xlsx
+++ b/todo_list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/avisek/Git_Repositary/DecodeLabs-Internship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC693AA-B908-A040-B24B-AF2C8988BBE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822BEA0D-11BE-A341-B9BC-8B540AB2CCC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
   <si>
     <t>Task ID</t>
   </si>
@@ -69,17 +69,43 @@
     <t>Assign Date</t>
   </si>
   <si>
-    <t>DCLB_DA001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missing Values replaced by Forword Fill Method
+    <t>DA001</t>
+  </si>
+  <si>
+    <t>DCLB-P1</t>
+  </si>
+  <si>
+    <t>Project 2</t>
+  </si>
+  <si>
+    <t>DA002</t>
+  </si>
+  <si>
+    <t>Exploratory Data Analysis (EDA)
+Goal:
+Analyze a dataset to understand
+patterns, trends, and
+distributions.
+Key Requirements:
+• Calculate basic statistics
+(mean, median, count)
+• Identify trends and outliers
+• Summarize key observations
+Key Skills:
+Data analysis, descriptive
+statistics, analytical thinking</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Missing Values replaced by No Coupon
 No Duplicates found
 Data formats okay
-outliers detected &amp; removed with upper bound 
+outliers detected &amp; Cap outliers for premium customer identification
 Histogram for data distribution
 Correlation
 Used Python for data cleaning
-File saved as dataset for Data Analysis_V1.1.xlsx
 </t>
   </si>
 </sst>
@@ -128,13 +154,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -143,6 +164,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -446,86 +470,132 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="56.6640625" style="2" customWidth="1"/>
-    <col min="3" max="7" width="20.83203125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="65.83203125" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="8.83203125" style="2"/>
+    <col min="1" max="1" width="14.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="56.6640625" style="1" customWidth="1"/>
+    <col min="3" max="7" width="20.83203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="65.83203125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>46101</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <v>46101</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <v>46101</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="221" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="2">
         <v>46105</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="2">
         <v>46106</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="2">
         <v>46109</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="2">
+        <v>46106</v>
+      </c>
+      <c r="F4" s="2">
+        <v>46106</v>
+      </c>
+      <c r="G4" s="2">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="272" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2">
+        <v>46106</v>
+      </c>
+      <c r="G5" s="2">
+        <v>46112</v>
       </c>
     </row>
   </sheetData>

--- a/todo_list.xlsx
+++ b/todo_list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/avisek/Git_Repositary/DecodeLabs-Internship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822BEA0D-11BE-A341-B9BC-8B540AB2CCC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ECC78D6-400F-974A-8AA5-E87594537715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
   <si>
     <t>Task ID</t>
   </si>
@@ -96,17 +96,29 @@
 statistics, analytical thinking</t>
   </si>
   <si>
-    <t>In Progress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missing Values replaced by No Coupon
-No Duplicates found
-Data formats okay
-outliers detected &amp; Cap outliers for premium customer identification
-Histogram for data distribution
-Correlation
-Used Python for data cleaning
-</t>
+    <t>DCLB-P2</t>
+  </si>
+  <si>
+    <t>DCLB-P3</t>
+  </si>
+  <si>
+    <t>Project 3</t>
+  </si>
+  <si>
+    <t>DA003</t>
+  </si>
+  <si>
+    <t>Goal:
+Use SQL queries to extract
+insights from a dataset.
+Key Requirements:
+• Write SELECT queries
+• Use WHERE, ORDER BY, GROUP BY
+• Perform basic aggregations
+(COUNT, SUM, AVG)
+Key Skills:
+SQL fundamentals, querying
+data, filtering and grouping</t>
   </si>
 </sst>
 </file>
@@ -470,7 +482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.1640625" style="1" bestFit="1" customWidth="1"/>
@@ -551,13 +563,11 @@
       <c r="G3" s="2">
         <v>46109</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>15</v>
@@ -589,13 +599,59 @@
         <v>8</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2">
         <v>46106</v>
       </c>
       <c r="G5" s="2">
         <v>46112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="2">
+        <v>46109</v>
+      </c>
+      <c r="F6" s="2">
+        <v>46109</v>
+      </c>
+      <c r="G6" s="2">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="221" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46109</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46116</v>
+      </c>
+      <c r="G7" s="2">
+        <v>46116</v>
       </c>
     </row>
   </sheetData>

--- a/todo_list.xlsx
+++ b/todo_list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/avisek/Git_Repositary/DecodeLabs-Internship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ECC78D6-400F-974A-8AA5-E87594537715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E985516C-6641-3E44-B340-420CFC641AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="27">
   <si>
     <t>Task ID</t>
   </si>
@@ -119,6 +119,25 @@
 Key Skills:
 SQL fundamentals, querying
 data, filtering and grouping</t>
+  </si>
+  <si>
+    <t>DCLB-P4</t>
+  </si>
+  <si>
+    <t>Project 4</t>
+  </si>
+  <si>
+    <t>DA004</t>
+  </si>
+  <si>
+    <t>Goal:
+Create visual representations of data to communicate insights clearly.
+Key Requirements:
+Create charts(bar, line, pie, etc.)
+Choose appropiate visuals for data
+Highlight key insights
+Key Skills:
+Data visualisation, charts, storytelling with data</t>
   </si>
 </sst>
 </file>
@@ -482,7 +501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.1640625" style="1" bestFit="1" customWidth="1"/>
@@ -654,6 +673,52 @@
         <v>46116</v>
       </c>
     </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2">
+        <v>46118</v>
+      </c>
+      <c r="F8" s="2">
+        <v>46118</v>
+      </c>
+      <c r="G8" s="2">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="187" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="2">
+        <v>46118</v>
+      </c>
+      <c r="F9" s="2">
+        <v>46120</v>
+      </c>
+      <c r="G9" s="2">
+        <v>46132</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" sqref="C2:C100" xr:uid="{00000000-0002-0000-0000-000000000000}">
